--- a/results/log_pv_cap_baseline_effects.xlsx
+++ b/results/log_pv_cap_baseline_effects.xlsx
@@ -413,98 +413,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>total_ML_LagFE(SLX)_inverse_distance</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>direct_ML_LagFE(SLX)_inverse_distance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>indirect_ML_LagFE(SLX)_inverse_distance</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_ML_LagFE(SLX)_k_nearest</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>direct_ML_LagFE(SLX)_k_nearest</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>indirect_ML_LagFE(SLX)_k_nearest</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_ML_LagFE(SLX)_queen</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>direct_ML_LagFE(SLX)_queen</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>indirect_ML_LagFE(SLX)_queen</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>total_ML_LagFE_inverse_distance</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>direct_ML_LagFE_inverse_distance</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>indirect_ML_LagFE_inverse_distance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_ML_LagFE_k_nearest</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>direct_ML_LagFE_k_nearest</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>indirect_ML_LagFE_k_nearest</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>total_ML_LagFE_queen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>direct_ML_LagFE_queen</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>indirect_ML_LagFE_queen</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>total_ML_LagFE(SLX)_inverse_distance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>direct_ML_LagFE(SLX)_inverse_distance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>indirect_ML_LagFE(SLX)_inverse_distance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>total_ML_LagFE(SLX)_k_nearest</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>direct_ML_LagFE(SLX)_k_nearest</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>indirect_ML_LagFE(SLX)_k_nearest</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>total_ML_LagFE(SLX)_queen</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>direct_ML_LagFE(SLX)_queen</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>indirect_ML_LagFE(SLX)_queen</t>
         </is>
       </c>
     </row>
@@ -516,92 +516,92 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-2.912</t>
+          <t>6.109</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.501</t>
+          <t>-0.512</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.411</t>
+          <t>6.621</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>4.525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.989</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>4.586</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.354</t>
+          <t>4.353</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.722</t>
+          <t>0.090</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>4.263</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.989</t>
+          <t>-2.033</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.679</t>
+          <t>-0.382</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>6.668</t>
+          <t>-1.651</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4.622</t>
+          <t>3.147</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.221</t>
+          <t>2.057</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.842</t>
+          <t>1.090</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4.513</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2.824</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.495</t>
+          <t>0.647</t>
         </is>
       </c>
     </row>
@@ -613,189 +613,92 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.590</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>-0.262</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.271</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.433</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.270</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.164</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.418</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>0.145</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.342</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.277</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.278</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.250</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.223</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.276</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-0.053</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.029</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>irradiance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>-1181552454.414</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>-203344648.773</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-978207805.642</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-5720539854.508</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-3752132061.852</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-1968407792.656</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-3181998136.270</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2582312040.694</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-599686095.576</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-3831197711.058</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>205253449.514</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-4036451160.573</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>5347204457.045</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-6440356316.203</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>11787560773.249</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>17711775534.833</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-1825828723.661</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>19537604258.494</t>
+          <t>0.063</t>
         </is>
       </c>
     </row>
